--- a/계산모델_엑셀/레시피모델.xlsx
+++ b/계산모델_엑셀/레시피모델.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +125,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -585,6 +592,19 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bump 높이 h (µm)</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n"/>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>도면값(선택). kV·W는 직경보다 높이·적층이 좌우 — 두꺼우면 W 최적화 필요</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -621,9 +641,9 @@
         <f>IF(B5&lt;=53,보정계수!B9,IF(B5&gt;=119,보정계수!B11,보정계수!B10))</f>
         <v/>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>자재 크기대별 앵커(보정계수 시트). ★시작값일 뿐 — 아래 트림 절차로 확정</t>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>자재 크기대별 기준 kV(보정계수 시트). 크기 영향은 약함(7배 커져도 ~3kV). ★시작값일 뿐 — 아래 트림으로 확정</t>
         </is>
       </c>
     </row>
@@ -666,12 +686,13 @@
           <t>Power (W)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>고정 (3.5~4.5W 무효과 실측)</t>
+      <c r="B15" s="8">
+        <f>IF(OR(B9="",B9&lt;=60),보정계수!B15,보정계수!B16)</f>
+        <v/>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>얇은 범프는 4W. 두꺼운 범프(높이 큼)는 PhaseW로 최적화된 값(보정계수 시트) — 더 이상 고정 아님</t>
         </is>
       </c>
     </row>
@@ -798,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -815,9 +836,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>상태: 검증됨(녹색 텍스트) / 잠정(빨강) — 잠정값은 실험 후 갱신하면 레시피계산이 자동 반영됨</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>상태: 검증됨 / 잠정 — 잠정값은 실험 후 갱신하면 레시피계산이 자동 반영됨. (W는 두꺼운 범프에서 최적화 대상 = 고정 아님)</t>
         </is>
       </c>
     </row>
@@ -909,7 +930,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>kV 앵커: 소형(≤53µm)</t>
+          <t>kV 기준값: 얇은/작은 범프(≤53µm)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -929,7 +950,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>kV 앵커: 중형(53~119µm)</t>
+          <t>kV 기준값: 중간(53~119µm)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -949,7 +970,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>kV 앵커: 대형(≥119µm)</t>
+          <t>kV 기준값: 두꺼운/큰 범프(≥119µm)</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -960,9 +981,9 @@
           <t>잠정</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>182µm 유사체 Q=101.7 역산. A2·A3(158µm 60/63kV)으로 확정</t>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>182µm 유사체 Q=101.7 역산. 158µm 자재로 확정 예정(PhaseA 60·63kV 2점)</t>
         </is>
       </c>
     </row>
@@ -1006,6 +1027,46 @@
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W: 얇은 범프(높이 ≤~60µm)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>검증됨</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>3.5~4.5W에서 내부 std 동일 → 둔감. 4W 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W: 두꺼운 범프(158µm급)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>잠정</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>PhaseW에서 깜빡임 void=0 &amp; void%σ 최소가 되는 W로 확정(잠정 5W). 고정값 아님</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1115,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>X-ray 광량. 3.5~4.5W에서 화질·시간에 영향 없음이 실측됨 → 4W 고정. 직경/대비 문제를 W로 고치려 하지 말 것(kV의 일).</t>
+          <t>X-ray 광량(선속). 광자가 부족한 '두꺼운 범프 내부'의 노이즈를 줄이는 변수. 얇은 범프(26µm)는 내부도 밝아 W에 둔감→4W. 두꺼운 범프(158µm)는 최적 W를 실험(PhaseW)으로 찾음(고정 아님). 직경/대비 문제는 W가 아니라 kV로 조절. W를 올리면 같은 품질을 더 적은 Frame(=시간↓)으로 얻는 교환도 가능.</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1224,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>[신규 자재만] WS Recipes 화면: 도면값(Bump Diameter/Pitch, Die Size)과 위 취득 파라미터(kV·R_acq·Frame32) 입력 → Create WS Recipe</t>
+          <t>[신규 자재만] WS Recipes 화면: 도면값(Bump Diameter/Pitch, Die Size)과 취득 파라미터(kV·R_acq·Frame32·W) 입력 → Create WS Recipe</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1260,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Die CAD &gt; Analysis Settings: 검사 파라미터(kV·R·Frame) 입력, Void Thresholds에 p% 설정 → Save</t>
+          <t>Die CAD &gt; Analysis Settings: 검사 파라미터(kV·R·Frame·W) 입력, Void Thresholds에 p% 설정 → Save (두꺼운 범프는 W를 PhaseW 최적값으로)</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/레시피모델.xlsx
+++ b/계산모델_엑셀/레시피모델.xlsx
@@ -55,7 +55,7 @@
       <color rgb="00007000"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +80,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +149,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -787,12 +805,12 @@
         </is>
       </c>
       <c r="B24" s="9">
-        <f>ROUND(보정계수!B13*(B6*B7)/(B11^2)*B14+보정계수!B14,0)</f>
+        <f>ROUND(B33*보정계수!B13*B14+보정계수!B14,0)</f>
         <v/>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>tact = a·(die면적/R²)·F + b — 계수 a,b는 실험 타임스탬프 회귀로 확정</t>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>tact ≈ (필요 shot 수) × (shot당 시간계수 a × Frame) + 오버헤드 b. 계수 a,b는 실험 타임스탬프 회귀로 확정</t>
         </is>
       </c>
     </row>
@@ -808,7 +826,110 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>■ 검사량 / shot 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>검사할 범프 수(목표)</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>이번 검사가 커버할 범프 수(자재·고객 요구)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>범프 pitch (µm)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>도면값</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>[기준] R0.2·pitch100 shot당 범프</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>★장비 실측 보정점(R0.2에서 한 번에 몇 개 잡히는지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>shot당 범프 수 @검사R</t>
+        </is>
+      </c>
+      <c r="B32" s="19">
+        <f>ROUND(B31*(B11/0.2)^2*(100/B30)^2,0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>R²·(1/pitch²)에 비례. B11=검사 Resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>필요 shot 수</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>ROUNDUP(B29/B32,0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>검사시간은 shot 수에 비례</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>※ 실험 일관성</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>R을 넓게 바꾸며 같은 범프를 볼 때는 '가장 작은 R에서도 1 shot에 들어오는 중앙 범프'만 추적할 것. 타일(여러 shot)이 섞이면 경계 잘림·콘빔 가장자리 왜곡·스티칭으로 R 비교가 오염됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A36:D38"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -993,7 +1114,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>tact 계수 a</t>
+          <t>tact 계수 a (shot·Frame당 초)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -1004,9 +1125,9 @@
           <t>잠정</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>tact=a·(die면적mm²/R²)·F+b — 전 런 타임스탬프 회귀로 확정</t>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>tact = a·(shot수·Frame) + b. 전 런 타임스탬프 회귀로 확정</t>
         </is>
       </c>
     </row>
@@ -1024,9 +1145,9 @@
           <t>잠정</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>〃</t>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>정렬·이동 등 shot 무관 고정시간</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/레시피모델.xlsx
+++ b/계산모델_엑셀/레시피모델.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +152,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -805,7 +809,7 @@
         </is>
       </c>
       <c r="B24" s="9">
-        <f>ROUND(B33*보정계수!B13*B14+보정계수!B14,0)</f>
+        <f>ROUND(B32*보정계수!B13*B14+보정계수!B14,0)</f>
         <v/>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -849,86 +853,75 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>범프 pitch (µm)</t>
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>[기준] R0.2 shot당 범프 수</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>도면값</t>
+          <t>※ 미확정 예시치 — 실제 R0.2 화면에서 shot당 범프 수를 세어 갱신할 것. pitch차이는 검사성공률 영향이 작다고 보아 미반영.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[기준] R0.2·pitch100 shot당 범프</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>50</v>
+          <t>shot당 범프 수 @검사R</t>
+        </is>
+      </c>
+      <c r="B31" s="19">
+        <f>ROUND(B30*(B11/0.2)^2,0)</f>
+        <v/>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>★장비 실측 보정점(R0.2에서 한 번에 몇 개 잡히는지)</t>
+          <t>R²에만 비례(FOV 면적). B11=검사 Resolution</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>shot당 범프 수 @검사R</t>
+          <t>필요 shot 수</t>
         </is>
       </c>
       <c r="B32" s="19">
-        <f>ROUND(B31*(B11/0.2)^2*(100/B30)^2,0)</f>
+        <f>ROUNDUP(B29/B31,0)</f>
         <v/>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>R²·(1/pitch²)에 비례. B11=검사 Resolution</t>
+          <t>검사시간은 shot 수에 비례</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>필요 shot 수</t>
-        </is>
-      </c>
-      <c r="B33" s="19">
-        <f>ROUNDUP(B29/B32,0)</f>
-        <v/>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>검사시간은 shot 수에 비례</t>
+      <c r="D33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>※ 실험 일관성</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>※ 실험 일관성</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>R을 넓게 바꾸며 같은 범프를 볼 때는 '가장 작은 R에서도 1 shot에 들어오는 중앙 범프'만 추적할 것. 타일(여러 shot)이 섞이면 경계 잘림·콘빔 가장자리 왜곡·스티칭으로 R 비교가 오염됨.</t>
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37"/>
     <row r="38"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:D38"/>
+    <mergeCell ref="A35:D37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/계산모델_엑셀/레시피모델.xlsx
+++ b/계산모델_엑셀/레시피모델.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -769,9 +769,9 @@
       <c r="B20" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>검증됨 (취득시간 절반). 추후 16 시도</t>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>검증됨(취득시간 절반, F32). 장비 F 최소=32라 더 낮출 수 없음</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,6 @@
     </row>
     <row r="36"/>
     <row r="37"/>
-    <row r="38"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A35:D37"/>
@@ -1032,9 +1031,9 @@
           <t>잠정</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>F1·F2(16/64)와 B2(32)의 void%σ 비교로 확정</t>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>F 스윕(32·64·128)의 void%σ 비교로 확정. 장비 F 최소=32</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1252,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>같은 장면을 여러 장 찍어 평균 → 노이즈 감소(∝1/√F), 시간 정비례. 취득은 32, 검사는 F_min.</t>
+          <t>같은 장면을 여러 장 찍어 평균 → 노이즈 감소(∝1/√F), 시간 정비례. 취득은 32, 검사는 F_min(장비 최소 32).</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/레시피모델.xlsx
+++ b/계산모델_엑셀/레시피모델.xlsx
@@ -647,9 +647,9 @@
         <f>ROUND(B5*SQRT(B8/100)/보정계수!B5,2)</f>
         <v/>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>R = D·√p / N_target. void 하나를 N픽셀 이상으로 담는 가장 거친(빠른) 해상도</t>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>R = D·√p / N_target(≈29). 정확도(총오차≤10%) 지키는 가장 거친(빠른) 해상도. 더 키우면 부정확</t>
         </is>
       </c>
     </row>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
           <t>잠정</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>이론 2/ε(ε=10%). Phase B(R스윕)에서 void% 안정화 지점으로 실측 확정</t>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>정확도=총오차10%=픽셀화(2/N≤7%,N≈29)⊕노이즈(2σ≤7%). Phase B(R스윕)+재현성(σ)으로 확정</t>
         </is>
       </c>
     </row>
